--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8765" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8765" uniqueCount="892">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1378,6 +1378,9 @@
 Occurrence Codes
 Value codes
 </t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>Supporting information</t>
@@ -12051,7 +12054,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>77</v>
@@ -12069,16 +12072,16 @@
         <v>269</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12115,7 +12118,7 @@
         <v>20</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
@@ -12148,10 +12151,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12254,10 +12257,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12362,10 +12365,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12472,10 +12475,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12501,14 +12504,14 @@
         <v>403</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12557,7 +12560,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>84</v>
@@ -12580,10 +12583,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12609,16 +12612,16 @@
         <v>159</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12646,10 +12649,10 @@
         <v>257</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12667,7 +12670,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>84</v>
@@ -12690,10 +12693,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12719,14 +12722,14 @@
         <v>159</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12754,10 +12757,10 @@
         <v>257</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -12775,7 +12778,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12798,10 +12801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12904,10 +12907,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13012,10 +13015,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13079,7 +13082,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13120,10 +13123,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13230,10 +13233,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13256,13 +13259,13 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13313,7 +13316,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -13336,10 +13339,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13362,19 +13365,19 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13423,7 +13426,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13446,10 +13449,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13475,16 +13478,16 @@
         <v>159</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13512,10 +13515,10 @@
         <v>257</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>20</v>
@@ -13533,7 +13536,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13556,20 +13559,20 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>431</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>77</v>
@@ -13587,16 +13590,16 @@
         <v>269</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -13668,10 +13671,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13774,10 +13777,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13882,10 +13885,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13992,10 +13995,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14021,14 +14024,14 @@
         <v>403</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -14077,7 +14080,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>84</v>
@@ -14100,10 +14103,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14129,16 +14132,16 @@
         <v>159</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14148,7 +14151,7 @@
         <v>20</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>20</v>
@@ -14166,10 +14169,10 @@
         <v>257</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>20</v>
@@ -14187,7 +14190,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>84</v>
@@ -14210,10 +14213,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14239,14 +14242,14 @@
         <v>159</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -14275,7 +14278,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>20</v>
@@ -14293,7 +14296,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -14311,15 +14314,15 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14422,10 +14425,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14530,10 +14533,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14597,7 +14600,7 @@
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>20</v>
@@ -14638,10 +14641,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14748,10 +14751,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14777,10 +14780,10 @@
         <v>211</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14819,17 +14822,17 @@
         <v>20</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14852,13 +14855,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>20</v>
@@ -14883,10 +14886,10 @@
         <v>211</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14937,7 +14940,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14955,15 +14958,15 @@
         <v>20</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14986,19 +14989,19 @@
         <v>20</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>20</v>
@@ -15047,7 +15050,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -15070,10 +15073,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15099,16 +15102,16 @@
         <v>159</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -15136,10 +15139,10 @@
         <v>257</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -15157,7 +15160,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -15180,13 +15183,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>431</v>
@@ -15211,16 +15214,16 @@
         <v>269</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -15292,10 +15295,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15398,10 +15401,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15506,10 +15509,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15616,10 +15619,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15645,14 +15648,14 @@
         <v>403</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -15701,7 +15704,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>84</v>
@@ -15724,10 +15727,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15753,16 +15756,16 @@
         <v>159</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>20</v>
@@ -15772,7 +15775,7 @@
         <v>20</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>20</v>
@@ -15790,10 +15793,10 @@
         <v>257</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>20</v>
@@ -15811,7 +15814,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>84</v>
@@ -15834,10 +15837,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15863,14 +15866,14 @@
         <v>159</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -15898,10 +15901,10 @@
         <v>257</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>20</v>
@@ -15919,7 +15922,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15942,10 +15945,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16048,10 +16051,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16156,10 +16159,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16223,7 +16226,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>20</v>
@@ -16264,10 +16267,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16374,10 +16377,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16400,13 +16403,13 @@
         <v>20</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16457,7 +16460,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16480,10 +16483,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16509,16 +16512,16 @@
         <v>413</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>20</v>
@@ -16567,7 +16570,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16585,15 +16588,15 @@
         <v>20</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16619,16 +16622,16 @@
         <v>159</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -16656,10 +16659,10 @@
         <v>257</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>20</v>
@@ -16677,7 +16680,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16700,13 +16703,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>431</v>
@@ -16731,16 +16734,16 @@
         <v>269</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>20</v>
@@ -16812,10 +16815,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16918,10 +16921,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17026,10 +17029,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17136,10 +17139,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17165,14 +17168,14 @@
         <v>403</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -17221,7 +17224,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>84</v>
@@ -17244,10 +17247,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17273,16 +17276,16 @@
         <v>159</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>20</v>
@@ -17292,7 +17295,7 @@
         <v>20</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>20</v>
@@ -17310,10 +17313,10 @@
         <v>257</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>20</v>
@@ -17331,7 +17334,7 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>84</v>
@@ -17354,10 +17357,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17383,14 +17386,14 @@
         <v>159</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -17418,10 +17421,10 @@
         <v>257</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>20</v>
@@ -17439,7 +17442,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17462,10 +17465,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17568,10 +17571,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17676,10 +17679,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17743,7 +17746,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>20</v>
@@ -17784,10 +17787,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17894,10 +17897,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17920,13 +17923,13 @@
         <v>20</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17977,7 +17980,7 @@
         <v>20</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -18000,10 +18003,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18026,19 +18029,19 @@
         <v>20</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -18075,7 +18078,7 @@
         <v>20</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AC138" s="2"/>
       <c r="AD138" t="s" s="2">
@@ -18085,7 +18088,7 @@
         <v>174</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -18108,13 +18111,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>20</v>
@@ -18136,19 +18139,19 @@
         <v>20</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -18197,7 +18200,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -18220,10 +18223,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18326,10 +18329,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18434,10 +18437,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18460,19 +18463,19 @@
         <v>85</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L142" t="s" s="2">
         <v>227</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -18521,7 +18524,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18544,10 +18547,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18573,20 +18576,20 @@
         <v>104</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q143" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="R143" t="s" s="2">
         <v>20</v>
@@ -18610,10 +18613,10 @@
         <v>108</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>20</v>
@@ -18631,7 +18634,7 @@
         <v>20</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -18654,10 +18657,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18683,14 +18686,14 @@
         <v>185</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>20</v>
@@ -18700,7 +18703,7 @@
         <v>20</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>20</v>
@@ -18739,7 +18742,7 @@
         <v>20</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -18762,10 +18765,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18791,14 +18794,14 @@
         <v>98</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>20</v>
@@ -18808,7 +18811,7 @@
         <v>20</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>20</v>
@@ -18847,7 +18850,7 @@
         <v>20</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -18856,7 +18859,7 @@
         <v>84</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>96</v>
@@ -18870,10 +18873,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18899,16 +18902,16 @@
         <v>104</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>20</v>
@@ -18918,7 +18921,7 @@
         <v>20</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>20</v>
@@ -18957,7 +18960,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -18966,7 +18969,7 @@
         <v>84</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>96</v>
@@ -18980,10 +18983,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19009,16 +19012,16 @@
         <v>159</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>20</v>
@@ -19046,10 +19049,10 @@
         <v>257</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>20</v>
@@ -19067,7 +19070,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19090,10 +19093,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19119,14 +19122,14 @@
         <v>269</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>20</v>
@@ -19175,7 +19178,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19198,10 +19201,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19304,10 +19307,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19412,10 +19415,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19522,10 +19525,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19551,16 +19554,16 @@
         <v>403</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>20</v>
@@ -19609,7 +19612,7 @@
         <v>20</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>84</v>
@@ -19632,10 +19635,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19658,17 +19661,17 @@
         <v>20</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>20</v>
@@ -19717,7 +19720,7 @@
         <v>20</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>84</v>
@@ -19740,10 +19743,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19769,16 +19772,16 @@
         <v>159</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>20</v>
@@ -19806,10 +19809,10 @@
         <v>257</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>20</v>
@@ -19827,7 +19830,7 @@
         <v>20</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19850,10 +19853,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19879,14 +19882,14 @@
         <v>159</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>20</v>
@@ -19914,10 +19917,10 @@
         <v>257</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>20</v>
@@ -19935,7 +19938,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -19958,10 +19961,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19987,14 +19990,14 @@
         <v>269</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>20</v>
@@ -20043,7 +20046,7 @@
         <v>20</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -20066,10 +20069,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20172,10 +20175,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20280,10 +20283,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20390,10 +20393,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20419,14 +20422,14 @@
         <v>403</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>20</v>
@@ -20475,7 +20478,7 @@
         <v>20</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>84</v>
@@ -20498,10 +20501,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20527,16 +20530,16 @@
         <v>159</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -20564,10 +20567,10 @@
         <v>257</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>20</v>
@@ -20585,7 +20588,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20608,10 +20611,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20637,14 +20640,14 @@
         <v>219</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>20</v>
@@ -20693,7 +20696,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20716,10 +20719,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20742,17 +20745,17 @@
         <v>20</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>20</v>
@@ -20780,10 +20783,10 @@
         <v>257</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>20</v>
@@ -20801,7 +20804,7 @@
         <v>20</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>84</v>
@@ -20824,10 +20827,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20850,17 +20853,17 @@
         <v>20</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>20</v>
@@ -20909,7 +20912,7 @@
         <v>20</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -20932,10 +20935,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20961,16 +20964,16 @@
         <v>269</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>20</v>
@@ -21019,7 +21022,7 @@
         <v>20</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -21042,10 +21045,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21148,10 +21151,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21256,10 +21259,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21366,10 +21369,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21395,14 +21398,14 @@
         <v>403</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>20</v>
@@ -21451,7 +21454,7 @@
         <v>20</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>84</v>
@@ -21474,10 +21477,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21503,16 +21506,16 @@
         <v>413</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>20</v>
@@ -21561,7 +21564,7 @@
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>84</v>
@@ -21584,10 +21587,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21613,16 +21616,16 @@
         <v>143</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>20</v>
@@ -21671,7 +21674,7 @@
         <v>20</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>76</v>
@@ -21694,10 +21697,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21720,17 +21723,17 @@
         <v>85</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>20</v>
@@ -21779,7 +21782,7 @@
         <v>20</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>84</v>
@@ -21802,10 +21805,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21831,14 +21834,14 @@
         <v>185</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>20</v>
@@ -21887,7 +21890,7 @@
         <v>20</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -21910,10 +21913,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21939,16 +21942,16 @@
         <v>185</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>20</v>
@@ -21997,7 +22000,7 @@
         <v>20</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
@@ -22020,10 +22023,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22046,19 +22049,19 @@
         <v>20</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>20</v>
@@ -22107,7 +22110,7 @@
         <v>20</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22130,10 +22133,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22159,14 +22162,14 @@
         <v>269</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>20</v>
@@ -22215,7 +22218,7 @@
         <v>20</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22238,10 +22241,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22344,10 +22347,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22452,10 +22455,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22562,10 +22565,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22588,19 +22591,19 @@
         <v>20</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>20</v>
@@ -22649,7 +22652,7 @@
         <v>20</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>84</v>
@@ -22667,15 +22670,15 @@
         <v>20</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22701,14 +22704,14 @@
         <v>159</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>20</v>
@@ -22737,7 +22740,7 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>20</v>
@@ -22755,7 +22758,7 @@
         <v>20</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22773,15 +22776,15 @@
         <v>20</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22804,17 +22807,17 @@
         <v>20</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>20</v>
@@ -22863,7 +22866,7 @@
         <v>20</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -22886,10 +22889,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -22912,17 +22915,17 @@
         <v>20</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>20</v>
@@ -22971,7 +22974,7 @@
         <v>20</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -22994,10 +22997,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23023,14 +23026,14 @@
         <v>269</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>20</v>
@@ -23079,7 +23082,7 @@
         <v>20</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23102,10 +23105,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23208,10 +23211,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23316,10 +23319,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23426,10 +23429,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23455,14 +23458,14 @@
         <v>403</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>20</v>
@@ -23511,7 +23514,7 @@
         <v>20</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>84</v>
@@ -23534,10 +23537,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23619,7 +23622,7 @@
         <v>20</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>76</v>
@@ -23642,10 +23645,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23671,14 +23674,14 @@
         <v>403</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>20</v>
@@ -23727,7 +23730,7 @@
         <v>20</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -23750,10 +23753,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23779,14 +23782,14 @@
         <v>403</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>20</v>
@@ -23835,7 +23838,7 @@
         <v>20</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>76</v>
@@ -23858,10 +23861,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23887,14 +23890,14 @@
         <v>403</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>20</v>
@@ -23943,7 +23946,7 @@
         <v>20</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>76</v>
@@ -23966,10 +23969,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23995,14 +23998,14 @@
         <v>403</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>20</v>
@@ -24051,7 +24054,7 @@
         <v>20</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>76</v>
@@ -24074,10 +24077,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24103,14 +24106,14 @@
         <v>159</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>20</v>
@@ -24138,10 +24141,10 @@
         <v>257</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>20</v>
@@ -24159,7 +24162,7 @@
         <v>20</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>76</v>
@@ -24182,10 +24185,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24211,16 +24214,16 @@
         <v>159</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>20</v>
@@ -24248,10 +24251,10 @@
         <v>257</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>20</v>
@@ -24269,7 +24272,7 @@
         <v>20</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>76</v>
@@ -24292,14 +24295,14 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
@@ -24321,16 +24324,16 @@
         <v>159</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>20</v>
@@ -24358,10 +24361,10 @@
         <v>257</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>20</v>
@@ -24379,7 +24382,7 @@
         <v>20</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>76</v>
@@ -24402,14 +24405,14 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
@@ -24431,10 +24434,10 @@
         <v>159</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -24465,7 +24468,7 @@
       </c>
       <c r="Y197" s="2"/>
       <c r="Z197" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>20</v>
@@ -24483,7 +24486,7 @@
         <v>20</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>76</v>
@@ -24506,10 +24509,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24532,17 +24535,17 @@
         <v>20</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>20</v>
@@ -24591,7 +24594,7 @@
         <v>20</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>76</v>
@@ -24614,10 +24617,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24643,16 +24646,16 @@
         <v>159</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>20</v>
@@ -24680,10 +24683,10 @@
         <v>257</v>
       </c>
       <c r="Y199" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Z199" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>20</v>
@@ -24701,7 +24704,7 @@
         <v>20</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>76</v>
@@ -24724,10 +24727,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24753,16 +24756,16 @@
         <v>159</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>20</v>
@@ -24790,10 +24793,10 @@
         <v>257</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>20</v>
@@ -24811,7 +24814,7 @@
         <v>20</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>76</v>
@@ -24834,10 +24837,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24860,17 +24863,17 @@
         <v>20</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>20</v>
@@ -24919,7 +24922,7 @@
         <v>20</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>76</v>
@@ -24942,10 +24945,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24968,17 +24971,17 @@
         <v>20</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>20</v>
@@ -25006,10 +25009,10 @@
         <v>257</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>20</v>
@@ -25027,7 +25030,7 @@
         <v>20</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>76</v>
@@ -25050,10 +25053,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25076,17 +25079,17 @@
         <v>20</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>20</v>
@@ -25135,7 +25138,7 @@
         <v>20</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>76</v>
@@ -25158,10 +25161,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25184,17 +25187,17 @@
         <v>20</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>20</v>
@@ -25243,7 +25246,7 @@
         <v>20</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>76</v>
@@ -25266,10 +25269,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25292,17 +25295,17 @@
         <v>20</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>20</v>
@@ -25351,7 +25354,7 @@
         <v>20</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>76</v>
@@ -25374,10 +25377,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25400,19 +25403,19 @@
         <v>20</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O206" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>20</v>
@@ -25461,7 +25464,7 @@
         <v>20</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>76</v>
@@ -25484,10 +25487,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25510,17 +25513,17 @@
         <v>20</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>20</v>
@@ -25569,7 +25572,7 @@
         <v>20</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>76</v>
@@ -25592,10 +25595,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25618,19 +25621,19 @@
         <v>20</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>20</v>
@@ -25679,7 +25682,7 @@
         <v>20</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>76</v>
@@ -25702,10 +25705,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25728,17 +25731,17 @@
         <v>20</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25787,7 +25790,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>76</v>
@@ -25810,10 +25813,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25839,10 +25842,10 @@
         <v>269</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -25893,7 +25896,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>76</v>
@@ -25916,10 +25919,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -26022,10 +26025,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26130,10 +26133,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26240,10 +26243,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26266,19 +26269,19 @@
         <v>20</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>20</v>
@@ -26307,7 +26310,7 @@
       </c>
       <c r="Y214" s="2"/>
       <c r="Z214" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>20</v>
@@ -26325,7 +26328,7 @@
         <v>20</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>84</v>
@@ -26348,10 +26351,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26377,14 +26380,14 @@
         <v>159</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>20</v>
@@ -26413,7 +26416,7 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>20</v>
@@ -26431,7 +26434,7 @@
         <v>20</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -26454,10 +26457,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26541,7 +26544,7 @@
         <v>20</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>76</v>
@@ -26564,10 +26567,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26593,14 +26596,14 @@
         <v>269</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>20</v>
@@ -26649,7 +26652,7 @@
         <v>20</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>76</v>
@@ -26672,10 +26675,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26778,10 +26781,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26886,10 +26889,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26996,10 +26999,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -27025,14 +27028,14 @@
         <v>403</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>20</v>
@@ -27081,7 +27084,7 @@
         <v>20</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>84</v>
@@ -27104,10 +27107,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -27189,7 +27192,7 @@
         <v>20</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>76</v>
@@ -27212,10 +27215,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -27241,14 +27244,14 @@
         <v>159</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>20</v>
@@ -27276,10 +27279,10 @@
         <v>257</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>20</v>
@@ -27297,7 +27300,7 @@
         <v>20</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>76</v>
@@ -27320,10 +27323,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27349,16 +27352,16 @@
         <v>159</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O224" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>20</v>
@@ -27386,10 +27389,10 @@
         <v>257</v>
       </c>
       <c r="Y224" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Z224" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AA224" t="s" s="2">
         <v>20</v>
@@ -27407,7 +27410,7 @@
         <v>20</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>76</v>
@@ -27430,14 +27433,14 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" t="s" s="2">
@@ -27459,16 +27462,16 @@
         <v>159</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>20</v>
@@ -27496,10 +27499,10 @@
         <v>257</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>20</v>
@@ -27517,7 +27520,7 @@
         <v>20</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>76</v>
@@ -27540,14 +27543,14 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
@@ -27569,10 +27572,10 @@
         <v>159</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -27603,7 +27606,7 @@
       </c>
       <c r="Y226" s="2"/>
       <c r="Z226" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>20</v>
@@ -27621,7 +27624,7 @@
         <v>20</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>76</v>
@@ -27644,10 +27647,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27673,16 +27676,16 @@
         <v>159</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>20</v>
@@ -27710,10 +27713,10 @@
         <v>257</v>
       </c>
       <c r="Y227" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Z227" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA227" t="s" s="2">
         <v>20</v>
@@ -27731,7 +27734,7 @@
         <v>20</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>76</v>
@@ -27754,10 +27757,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27783,16 +27786,16 @@
         <v>159</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>20</v>
@@ -27820,10 +27823,10 @@
         <v>257</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>20</v>
@@ -27841,7 +27844,7 @@
         <v>20</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>76</v>
@@ -27864,10 +27867,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27890,17 +27893,17 @@
         <v>20</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>20</v>
@@ -27949,7 +27952,7 @@
         <v>20</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>76</v>
@@ -27972,10 +27975,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27998,17 +28001,17 @@
         <v>20</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>20</v>
@@ -28057,7 +28060,7 @@
         <v>20</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>76</v>
@@ -28080,10 +28083,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -28106,17 +28109,17 @@
         <v>20</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>20</v>
@@ -28165,7 +28168,7 @@
         <v>20</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>76</v>
@@ -28188,10 +28191,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -28214,19 +28217,19 @@
         <v>20</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>20</v>
@@ -28275,7 +28278,7 @@
         <v>20</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>76</v>
@@ -28298,10 +28301,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28324,17 +28327,17 @@
         <v>20</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>20</v>
@@ -28383,7 +28386,7 @@
         <v>20</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>76</v>
@@ -28406,10 +28409,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28432,19 +28435,19 @@
         <v>20</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>20</v>
@@ -28493,7 +28496,7 @@
         <v>20</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>76</v>
@@ -28516,10 +28519,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28542,17 +28545,17 @@
         <v>20</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>20</v>
@@ -28601,7 +28604,7 @@
         <v>20</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>76</v>
@@ -28624,10 +28627,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28653,14 +28656,14 @@
         <v>269</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>20</v>
@@ -28709,7 +28712,7 @@
         <v>20</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>76</v>
@@ -28732,10 +28735,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28838,10 +28841,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28946,10 +28949,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -29056,10 +29059,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -29085,14 +29088,14 @@
         <v>403</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>20</v>
@@ -29141,7 +29144,7 @@
         <v>20</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>84</v>
@@ -29164,10 +29167,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -29249,7 +29252,7 @@
         <v>20</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>76</v>
@@ -29272,10 +29275,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -29301,14 +29304,14 @@
         <v>159</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>20</v>
@@ -29336,10 +29339,10 @@
         <v>257</v>
       </c>
       <c r="Y242" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Z242" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AA242" t="s" s="2">
         <v>20</v>
@@ -29357,7 +29360,7 @@
         <v>20</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>76</v>
@@ -29380,10 +29383,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -29409,16 +29412,16 @@
         <v>159</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>20</v>
@@ -29446,10 +29449,10 @@
         <v>257</v>
       </c>
       <c r="Y243" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Z243" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>20</v>
@@ -29467,7 +29470,7 @@
         <v>20</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>76</v>
@@ -29490,10 +29493,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -29519,16 +29522,16 @@
         <v>159</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>20</v>
@@ -29556,10 +29559,10 @@
         <v>257</v>
       </c>
       <c r="Y244" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="Z244" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA244" t="s" s="2">
         <v>20</v>
@@ -29577,7 +29580,7 @@
         <v>20</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>76</v>
@@ -29600,14 +29603,14 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
@@ -29629,10 +29632,10 @@
         <v>159</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
@@ -29663,7 +29666,7 @@
       </c>
       <c r="Y245" s="2"/>
       <c r="Z245" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>20</v>
@@ -29681,7 +29684,7 @@
         <v>20</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>76</v>
@@ -29704,10 +29707,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -29733,16 +29736,16 @@
         <v>159</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>20</v>
@@ -29770,10 +29773,10 @@
         <v>257</v>
       </c>
       <c r="Y246" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Z246" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>20</v>
@@ -29791,7 +29794,7 @@
         <v>20</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>76</v>
@@ -29814,10 +29817,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -29843,16 +29846,16 @@
         <v>159</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>20</v>
@@ -29880,10 +29883,10 @@
         <v>257</v>
       </c>
       <c r="Y247" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>20</v>
@@ -29901,7 +29904,7 @@
         <v>20</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>76</v>
@@ -29924,10 +29927,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -29950,17 +29953,17 @@
         <v>20</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>20</v>
@@ -30009,7 +30012,7 @@
         <v>20</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>76</v>
@@ -30032,10 +30035,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -30058,17 +30061,17 @@
         <v>20</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="P249" t="s" s="2">
         <v>20</v>
@@ -30117,7 +30120,7 @@
         <v>20</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>76</v>
@@ -30140,10 +30143,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -30166,17 +30169,17 @@
         <v>20</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>20</v>
@@ -30225,7 +30228,7 @@
         <v>20</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>76</v>
@@ -30248,10 +30251,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -30274,19 +30277,19 @@
         <v>20</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O251" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>20</v>
@@ -30335,7 +30338,7 @@
         <v>20</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>76</v>
@@ -30358,10 +30361,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -30384,17 +30387,17 @@
         <v>20</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="P252" t="s" s="2">
         <v>20</v>
@@ -30443,7 +30446,7 @@
         <v>20</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>76</v>
@@ -30466,10 +30469,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -30492,19 +30495,19 @@
         <v>20</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O253" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="P253" t="s" s="2">
         <v>20</v>
@@ -30553,7 +30556,7 @@
         <v>20</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>76</v>
@@ -30576,10 +30579,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -30602,17 +30605,17 @@
         <v>20</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P254" t="s" s="2">
         <v>20</v>
@@ -30661,7 +30664,7 @@
         <v>20</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>76</v>
@@ -30684,10 +30687,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -30710,17 +30713,17 @@
         <v>20</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>20</v>
@@ -30769,7 +30772,7 @@
         <v>20</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>76</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8765" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8765" uniqueCount="893">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1853,6 +1853,9 @@
   </si>
   <si>
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -18921,7 +18924,7 @@
         <v>20</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>20</v>
@@ -18960,7 +18963,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -18983,7 +18986,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>473</v>
@@ -19093,10 +19096,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19122,14 +19125,14 @@
         <v>269</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>20</v>
@@ -19178,7 +19181,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19201,10 +19204,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19307,10 +19310,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19415,10 +19418,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19525,10 +19528,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19554,16 +19557,16 @@
         <v>403</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>20</v>
@@ -19612,7 +19615,7 @@
         <v>20</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>84</v>
@@ -19635,10 +19638,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19661,17 +19664,17 @@
         <v>20</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>20</v>
@@ -19720,7 +19723,7 @@
         <v>20</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>84</v>
@@ -19743,10 +19746,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19772,16 +19775,16 @@
         <v>159</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>20</v>
@@ -19809,10 +19812,10 @@
         <v>257</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>20</v>
@@ -19830,7 +19833,7 @@
         <v>20</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19853,10 +19856,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19882,14 +19885,14 @@
         <v>159</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>20</v>
@@ -19917,10 +19920,10 @@
         <v>257</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>20</v>
@@ -19938,7 +19941,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -19961,10 +19964,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19990,14 +19993,14 @@
         <v>269</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>20</v>
@@ -20046,7 +20049,7 @@
         <v>20</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -20069,10 +20072,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20175,10 +20178,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20283,10 +20286,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20393,10 +20396,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20422,14 +20425,14 @@
         <v>403</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>20</v>
@@ -20478,7 +20481,7 @@
         <v>20</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>84</v>
@@ -20501,10 +20504,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20530,16 +20533,16 @@
         <v>159</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -20567,10 +20570,10 @@
         <v>257</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>20</v>
@@ -20588,7 +20591,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20611,10 +20614,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20640,14 +20643,14 @@
         <v>219</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>20</v>
@@ -20696,7 +20699,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20719,10 +20722,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20745,17 +20748,17 @@
         <v>20</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>20</v>
@@ -20783,10 +20786,10 @@
         <v>257</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>20</v>
@@ -20804,7 +20807,7 @@
         <v>20</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>84</v>
@@ -20827,10 +20830,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20853,17 +20856,17 @@
         <v>20</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>20</v>
@@ -20912,7 +20915,7 @@
         <v>20</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -20935,10 +20938,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20964,16 +20967,16 @@
         <v>269</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>20</v>
@@ -21022,7 +21025,7 @@
         <v>20</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -21045,10 +21048,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21151,10 +21154,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21259,10 +21262,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21369,10 +21372,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21398,14 +21401,14 @@
         <v>403</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>20</v>
@@ -21454,7 +21457,7 @@
         <v>20</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>84</v>
@@ -21477,10 +21480,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21506,16 +21509,16 @@
         <v>413</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>20</v>
@@ -21564,7 +21567,7 @@
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>84</v>
@@ -21587,10 +21590,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21616,16 +21619,16 @@
         <v>143</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>20</v>
@@ -21674,7 +21677,7 @@
         <v>20</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>76</v>
@@ -21697,10 +21700,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21723,17 +21726,17 @@
         <v>85</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>20</v>
@@ -21782,7 +21785,7 @@
         <v>20</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>84</v>
@@ -21805,10 +21808,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21834,14 +21837,14 @@
         <v>185</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>20</v>
@@ -21890,7 +21893,7 @@
         <v>20</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -21913,10 +21916,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21942,16 +21945,16 @@
         <v>185</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>20</v>
@@ -22000,7 +22003,7 @@
         <v>20</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
@@ -22023,10 +22026,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22049,19 +22052,19 @@
         <v>20</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>20</v>
@@ -22110,7 +22113,7 @@
         <v>20</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22133,10 +22136,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22162,14 +22165,14 @@
         <v>269</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>20</v>
@@ -22218,7 +22221,7 @@
         <v>20</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22241,10 +22244,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22347,10 +22350,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22455,10 +22458,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22565,10 +22568,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22591,19 +22594,19 @@
         <v>20</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>20</v>
@@ -22652,7 +22655,7 @@
         <v>20</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>84</v>
@@ -22670,15 +22673,15 @@
         <v>20</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22704,14 +22707,14 @@
         <v>159</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>20</v>
@@ -22740,7 +22743,7 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>20</v>
@@ -22758,7 +22761,7 @@
         <v>20</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22776,15 +22779,15 @@
         <v>20</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22807,17 +22810,17 @@
         <v>20</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>20</v>
@@ -22866,7 +22869,7 @@
         <v>20</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -22889,10 +22892,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -22915,17 +22918,17 @@
         <v>20</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>20</v>
@@ -22974,7 +22977,7 @@
         <v>20</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -22997,10 +23000,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23026,14 +23029,14 @@
         <v>269</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>20</v>
@@ -23082,7 +23085,7 @@
         <v>20</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23105,10 +23108,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23211,10 +23214,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23319,10 +23322,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23429,10 +23432,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23458,14 +23461,14 @@
         <v>403</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>20</v>
@@ -23514,7 +23517,7 @@
         <v>20</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>84</v>
@@ -23537,10 +23540,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23622,7 +23625,7 @@
         <v>20</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>76</v>
@@ -23645,10 +23648,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23674,14 +23677,14 @@
         <v>403</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>20</v>
@@ -23730,7 +23733,7 @@
         <v>20</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -23753,10 +23756,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23782,14 +23785,14 @@
         <v>403</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>20</v>
@@ -23838,7 +23841,7 @@
         <v>20</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>76</v>
@@ -23861,10 +23864,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23890,14 +23893,14 @@
         <v>403</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>20</v>
@@ -23946,7 +23949,7 @@
         <v>20</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>76</v>
@@ -23969,10 +23972,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23998,14 +24001,14 @@
         <v>403</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>20</v>
@@ -24054,7 +24057,7 @@
         <v>20</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>76</v>
@@ -24077,10 +24080,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24106,14 +24109,14 @@
         <v>159</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>20</v>
@@ -24141,10 +24144,10 @@
         <v>257</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>20</v>
@@ -24162,7 +24165,7 @@
         <v>20</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>76</v>
@@ -24185,10 +24188,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24214,16 +24217,16 @@
         <v>159</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>20</v>
@@ -24251,10 +24254,10 @@
         <v>257</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>20</v>
@@ -24272,7 +24275,7 @@
         <v>20</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>76</v>
@@ -24295,14 +24298,14 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
@@ -24324,16 +24327,16 @@
         <v>159</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>20</v>
@@ -24361,10 +24364,10 @@
         <v>257</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>20</v>
@@ -24382,7 +24385,7 @@
         <v>20</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>76</v>
@@ -24405,14 +24408,14 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
@@ -24434,10 +24437,10 @@
         <v>159</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -24468,7 +24471,7 @@
       </c>
       <c r="Y197" s="2"/>
       <c r="Z197" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>20</v>
@@ -24486,7 +24489,7 @@
         <v>20</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>76</v>
@@ -24509,10 +24512,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24535,17 +24538,17 @@
         <v>20</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>20</v>
@@ -24594,7 +24597,7 @@
         <v>20</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>76</v>
@@ -24617,10 +24620,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24646,16 +24649,16 @@
         <v>159</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>20</v>
@@ -24683,10 +24686,10 @@
         <v>257</v>
       </c>
       <c r="Y199" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="Z199" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>20</v>
@@ -24704,7 +24707,7 @@
         <v>20</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>76</v>
@@ -24727,10 +24730,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24756,16 +24759,16 @@
         <v>159</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>20</v>
@@ -24793,10 +24796,10 @@
         <v>257</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>20</v>
@@ -24814,7 +24817,7 @@
         <v>20</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>76</v>
@@ -24837,10 +24840,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24866,14 +24869,14 @@
         <v>464</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>20</v>
@@ -24922,7 +24925,7 @@
         <v>20</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>76</v>
@@ -24945,10 +24948,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24971,17 +24974,17 @@
         <v>20</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>20</v>
@@ -25009,10 +25012,10 @@
         <v>257</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>20</v>
@@ -25030,7 +25033,7 @@
         <v>20</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>76</v>
@@ -25053,10 +25056,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25079,17 +25082,17 @@
         <v>20</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>20</v>
@@ -25138,7 +25141,7 @@
         <v>20</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>76</v>
@@ -25161,10 +25164,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25187,17 +25190,17 @@
         <v>20</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>20</v>
@@ -25246,7 +25249,7 @@
         <v>20</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>76</v>
@@ -25269,10 +25272,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25295,17 +25298,17 @@
         <v>20</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>20</v>
@@ -25354,7 +25357,7 @@
         <v>20</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>76</v>
@@ -25377,10 +25380,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25406,16 +25409,16 @@
         <v>548</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O206" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>20</v>
@@ -25464,7 +25467,7 @@
         <v>20</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>76</v>
@@ -25487,10 +25490,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25513,17 +25516,17 @@
         <v>20</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>20</v>
@@ -25572,7 +25575,7 @@
         <v>20</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>76</v>
@@ -25595,10 +25598,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25621,19 +25624,19 @@
         <v>20</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>20</v>
@@ -25682,7 +25685,7 @@
         <v>20</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>76</v>
@@ -25705,10 +25708,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25731,17 +25734,17 @@
         <v>20</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25790,7 +25793,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>76</v>
@@ -25813,10 +25816,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25842,10 +25845,10 @@
         <v>269</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -25896,7 +25899,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>76</v>
@@ -25919,10 +25922,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -26025,10 +26028,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26133,10 +26136,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26243,10 +26246,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26269,19 +26272,19 @@
         <v>20</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>20</v>
@@ -26310,7 +26313,7 @@
       </c>
       <c r="Y214" s="2"/>
       <c r="Z214" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>20</v>
@@ -26328,7 +26331,7 @@
         <v>20</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>84</v>
@@ -26351,10 +26354,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26380,14 +26383,14 @@
         <v>159</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>20</v>
@@ -26416,7 +26419,7 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>20</v>
@@ -26434,7 +26437,7 @@
         <v>20</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -26457,10 +26460,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26544,7 +26547,7 @@
         <v>20</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>76</v>
@@ -26567,10 +26570,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26596,14 +26599,14 @@
         <v>269</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>20</v>
@@ -26652,7 +26655,7 @@
         <v>20</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>76</v>
@@ -26675,10 +26678,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26781,10 +26784,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26889,10 +26892,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26999,10 +27002,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -27028,14 +27031,14 @@
         <v>403</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>20</v>
@@ -27084,7 +27087,7 @@
         <v>20</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>84</v>
@@ -27107,10 +27110,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -27192,7 +27195,7 @@
         <v>20</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>76</v>
@@ -27215,10 +27218,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -27244,14 +27247,14 @@
         <v>159</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>20</v>
@@ -27279,10 +27282,10 @@
         <v>257</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>20</v>
@@ -27300,7 +27303,7 @@
         <v>20</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>76</v>
@@ -27323,10 +27326,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27352,16 +27355,16 @@
         <v>159</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="O224" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>20</v>
@@ -27389,10 +27392,10 @@
         <v>257</v>
       </c>
       <c r="Y224" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Z224" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AA224" t="s" s="2">
         <v>20</v>
@@ -27410,7 +27413,7 @@
         <v>20</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>76</v>
@@ -27433,14 +27436,14 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" t="s" s="2">
@@ -27462,16 +27465,16 @@
         <v>159</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>20</v>
@@ -27499,10 +27502,10 @@
         <v>257</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>20</v>
@@ -27520,7 +27523,7 @@
         <v>20</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>76</v>
@@ -27543,14 +27546,14 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
@@ -27572,10 +27575,10 @@
         <v>159</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -27606,7 +27609,7 @@
       </c>
       <c r="Y226" s="2"/>
       <c r="Z226" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>20</v>
@@ -27624,7 +27627,7 @@
         <v>20</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>76</v>
@@ -27647,10 +27650,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27676,16 +27679,16 @@
         <v>159</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>20</v>
@@ -27713,10 +27716,10 @@
         <v>257</v>
       </c>
       <c r="Y227" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="Z227" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AA227" t="s" s="2">
         <v>20</v>
@@ -27734,7 +27737,7 @@
         <v>20</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>76</v>
@@ -27757,10 +27760,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27786,16 +27789,16 @@
         <v>159</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>20</v>
@@ -27823,10 +27826,10 @@
         <v>257</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>20</v>
@@ -27844,7 +27847,7 @@
         <v>20</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>76</v>
@@ -27867,10 +27870,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27893,17 +27896,17 @@
         <v>20</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>20</v>
@@ -27952,7 +27955,7 @@
         <v>20</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>76</v>
@@ -27975,10 +27978,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -28001,17 +28004,17 @@
         <v>20</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>20</v>
@@ -28060,7 +28063,7 @@
         <v>20</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>76</v>
@@ -28083,10 +28086,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -28109,17 +28112,17 @@
         <v>20</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>20</v>
@@ -28168,7 +28171,7 @@
         <v>20</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>76</v>
@@ -28191,10 +28194,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -28220,16 +28223,16 @@
         <v>548</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>20</v>
@@ -28278,7 +28281,7 @@
         <v>20</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>76</v>
@@ -28301,10 +28304,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28327,17 +28330,17 @@
         <v>20</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>20</v>
@@ -28386,7 +28389,7 @@
         <v>20</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>76</v>
@@ -28409,10 +28412,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28435,19 +28438,19 @@
         <v>20</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>20</v>
@@ -28496,7 +28499,7 @@
         <v>20</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>76</v>
@@ -28519,10 +28522,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28545,17 +28548,17 @@
         <v>20</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>20</v>
@@ -28604,7 +28607,7 @@
         <v>20</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>76</v>
@@ -28627,10 +28630,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28656,14 +28659,14 @@
         <v>269</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>20</v>
@@ -28712,7 +28715,7 @@
         <v>20</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>76</v>
@@ -28735,10 +28738,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28841,10 +28844,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28949,10 +28952,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -29059,10 +29062,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -29088,14 +29091,14 @@
         <v>403</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>20</v>
@@ -29144,7 +29147,7 @@
         <v>20</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>84</v>
@@ -29167,10 +29170,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -29252,7 +29255,7 @@
         <v>20</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>76</v>
@@ -29275,10 +29278,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -29304,14 +29307,14 @@
         <v>159</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>20</v>
@@ -29339,10 +29342,10 @@
         <v>257</v>
       </c>
       <c r="Y242" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Z242" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AA242" t="s" s="2">
         <v>20</v>
@@ -29360,7 +29363,7 @@
         <v>20</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>76</v>
@@ -29383,10 +29386,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -29412,16 +29415,16 @@
         <v>159</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>20</v>
@@ -29449,10 +29452,10 @@
         <v>257</v>
       </c>
       <c r="Y243" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Z243" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>20</v>
@@ -29470,7 +29473,7 @@
         <v>20</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>76</v>
@@ -29493,10 +29496,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -29522,16 +29525,16 @@
         <v>159</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>20</v>
@@ -29559,10 +29562,10 @@
         <v>257</v>
       </c>
       <c r="Y244" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Z244" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA244" t="s" s="2">
         <v>20</v>
@@ -29580,7 +29583,7 @@
         <v>20</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>76</v>
@@ -29603,14 +29606,14 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
@@ -29632,10 +29635,10 @@
         <v>159</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
@@ -29666,7 +29669,7 @@
       </c>
       <c r="Y245" s="2"/>
       <c r="Z245" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>20</v>
@@ -29684,7 +29687,7 @@
         <v>20</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>76</v>
@@ -29707,10 +29710,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -29736,16 +29739,16 @@
         <v>159</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>20</v>
@@ -29773,10 +29776,10 @@
         <v>257</v>
       </c>
       <c r="Y246" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="Z246" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>20</v>
@@ -29794,7 +29797,7 @@
         <v>20</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>76</v>
@@ -29817,10 +29820,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -29846,16 +29849,16 @@
         <v>159</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>20</v>
@@ -29883,10 +29886,10 @@
         <v>257</v>
       </c>
       <c r="Y247" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>20</v>
@@ -29904,7 +29907,7 @@
         <v>20</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>76</v>
@@ -29927,10 +29930,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -29953,17 +29956,17 @@
         <v>20</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>20</v>
@@ -30012,7 +30015,7 @@
         <v>20</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>76</v>
@@ -30035,10 +30038,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -30061,17 +30064,17 @@
         <v>20</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P249" t="s" s="2">
         <v>20</v>
@@ -30120,7 +30123,7 @@
         <v>20</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>76</v>
@@ -30143,10 +30146,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -30169,17 +30172,17 @@
         <v>20</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>20</v>
@@ -30228,7 +30231,7 @@
         <v>20</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>76</v>
@@ -30251,10 +30254,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -30280,16 +30283,16 @@
         <v>548</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O251" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>20</v>
@@ -30338,7 +30341,7 @@
         <v>20</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>76</v>
@@ -30361,10 +30364,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -30387,17 +30390,17 @@
         <v>20</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="P252" t="s" s="2">
         <v>20</v>
@@ -30446,7 +30449,7 @@
         <v>20</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>76</v>
@@ -30469,10 +30472,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -30495,19 +30498,19 @@
         <v>20</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="O253" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="P253" t="s" s="2">
         <v>20</v>
@@ -30556,7 +30559,7 @@
         <v>20</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>76</v>
@@ -30579,10 +30582,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -30605,17 +30608,17 @@
         <v>20</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P254" t="s" s="2">
         <v>20</v>
@@ -30664,7 +30667,7 @@
         <v>20</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>76</v>
@@ -30687,10 +30690,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -30713,17 +30716,17 @@
         <v>20</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>20</v>
@@ -30772,7 +30775,7 @@
         <v>20</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>76</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -798,7 +798,7 @@
     <t>Claim.provider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KHOrganization)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KAOrganization)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -666,7 +666,7 @@
     <t>Claim.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedPatient)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK|https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname)
 </t>
   </si>
   <si>
@@ -3111,7 +3111,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="116.35546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="118.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedVAERequestVerlaengerung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
